--- a/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Greenfield_Patagonien_Naphta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CADE91F-1880-4D44-82D0-537A8412F008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DF538-87C5-4D40-9FF2-29B2E1E1C79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="664" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="398">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1356,6 +1356,36 @@
   </si>
   <si>
     <t>Levelized Cost of FT (Kerosin+Naphtha)</t>
+  </si>
+  <si>
+    <t>Verkaufspreiseanalyse</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis Bilanznull</t>
+  </si>
+  <si>
+    <t>Verkaufspreis Bilanznull mit Vorverkauf</t>
+  </si>
+  <si>
+    <t>calc_maxprice</t>
+  </si>
+  <si>
+    <t>calc_price</t>
+  </si>
+  <si>
+    <t>calc_maxprice_h2</t>
+  </si>
+  <si>
+    <t>Maximaler Verkaufspreis H2</t>
+  </si>
+  <si>
+    <t>€/kg_h2</t>
+  </si>
+  <si>
+    <t>calc_optprice</t>
+  </si>
+  <si>
+    <t>Verkaufspreis bei optimalem Vorverkauf</t>
   </si>
 </sst>
 </file>
@@ -1586,7 +1616,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="113">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1669,6 +1699,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1723,23 +1754,32 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1747,32 +1787,11 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1782,6 +1801,24 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2316,10 +2353,10 @@
       <c r="G1" s="6"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="72" t="s">
+      <c r="A2" s="73" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="82" t="s">
+      <c r="B2" s="83" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2336,8 +2373,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="73"/>
-      <c r="B3" s="80"/>
+      <c r="A3" s="74"/>
+      <c r="B3" s="81"/>
       <c r="C3" t="s">
         <v>84</v>
       </c>
@@ -2352,8 +2389,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="73"/>
-      <c r="B4" s="80"/>
+      <c r="A4" s="74"/>
+      <c r="B4" s="81"/>
       <c r="C4" t="s">
         <v>10</v>
       </c>
@@ -2368,8 +2405,8 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="73"/>
-      <c r="B5" s="80"/>
+      <c r="A5" s="74"/>
+      <c r="B5" s="81"/>
       <c r="C5" t="s">
         <v>11</v>
       </c>
@@ -2384,8 +2421,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="73"/>
-      <c r="B6" s="80"/>
+      <c r="A6" s="74"/>
+      <c r="B6" s="81"/>
       <c r="C6" t="s">
         <v>13</v>
       </c>
@@ -2400,8 +2437,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="73"/>
-      <c r="B7" s="80"/>
+      <c r="A7" s="74"/>
+      <c r="B7" s="81"/>
       <c r="C7" t="s">
         <v>15</v>
       </c>
@@ -2416,8 +2453,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="73"/>
-      <c r="B8" s="83" t="s">
+      <c r="A8" s="74"/>
+      <c r="B8" s="84" t="s">
         <v>332</v>
       </c>
       <c r="C8" s="35" t="s">
@@ -2434,8 +2471,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="84"/>
+      <c r="A9" s="74"/>
+      <c r="B9" s="85"/>
       <c r="C9" s="13" t="s">
         <v>85</v>
       </c>
@@ -2450,8 +2487,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="73"/>
-      <c r="B10" s="84"/>
+      <c r="A10" s="74"/>
+      <c r="B10" s="85"/>
       <c r="C10" s="13" t="s">
         <v>10</v>
       </c>
@@ -2466,8 +2503,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="84"/>
+      <c r="A11" s="74"/>
+      <c r="B11" s="85"/>
       <c r="C11" s="13" t="s">
         <v>11</v>
       </c>
@@ -2482,8 +2519,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="73"/>
-      <c r="B12" s="84"/>
+      <c r="A12" s="74"/>
+      <c r="B12" s="85"/>
       <c r="C12" s="13" t="s">
         <v>86</v>
       </c>
@@ -2498,8 +2535,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="73"/>
-      <c r="B13" s="84"/>
+      <c r="A13" s="74"/>
+      <c r="B13" s="85"/>
       <c r="C13" s="13" t="s">
         <v>239</v>
       </c>
@@ -2514,8 +2551,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="73"/>
-      <c r="B14" s="84"/>
+      <c r="A14" s="74"/>
+      <c r="B14" s="85"/>
       <c r="C14" s="13" t="s">
         <v>370</v>
       </c>
@@ -2530,8 +2567,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="73"/>
-      <c r="B15" s="84"/>
+      <c r="A15" s="74"/>
+      <c r="B15" s="85"/>
       <c r="C15" s="13" t="s">
         <v>13</v>
       </c>
@@ -2546,8 +2583,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="73"/>
-      <c r="B16" s="85"/>
+      <c r="A16" s="74"/>
+      <c r="B16" s="86"/>
       <c r="C16" s="36" t="s">
         <v>15</v>
       </c>
@@ -2562,8 +2599,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="73"/>
-      <c r="B17" s="87" t="s">
+      <c r="A17" s="74"/>
+      <c r="B17" s="88" t="s">
         <v>264</v>
       </c>
       <c r="C17" s="35" t="s">
@@ -2580,8 +2617,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="73"/>
-      <c r="B18" s="88"/>
+      <c r="A18" s="74"/>
+      <c r="B18" s="89"/>
       <c r="C18" s="13" t="s">
         <v>84</v>
       </c>
@@ -2596,8 +2633,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="73"/>
-      <c r="B19" s="88"/>
+      <c r="A19" s="74"/>
+      <c r="B19" s="89"/>
       <c r="C19" s="13" t="s">
         <v>10</v>
       </c>
@@ -2612,8 +2649,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="88"/>
+      <c r="A20" s="74"/>
+      <c r="B20" s="89"/>
       <c r="C20" s="13" t="s">
         <v>11</v>
       </c>
@@ -2628,8 +2665,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="73"/>
-      <c r="B21" s="88"/>
+      <c r="A21" s="74"/>
+      <c r="B21" s="89"/>
       <c r="C21" s="13" t="s">
         <v>13</v>
       </c>
@@ -2644,8 +2681,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="73"/>
-      <c r="B22" s="89"/>
+      <c r="A22" s="74"/>
+      <c r="B22" s="90"/>
       <c r="C22" s="36" t="s">
         <v>15</v>
       </c>
@@ -2660,8 +2697,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="73"/>
-      <c r="B23" s="86" t="s">
+      <c r="A23" s="74"/>
+      <c r="B23" s="87" t="s">
         <v>231</v>
       </c>
       <c r="C23" s="44" t="s">
@@ -2678,8 +2715,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="73"/>
-      <c r="B24" s="86"/>
+      <c r="A24" s="74"/>
+      <c r="B24" s="87"/>
       <c r="C24" s="44" t="s">
         <v>272</v>
       </c>
@@ -2694,8 +2731,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
-      <c r="B25" s="86"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="87"/>
       <c r="C25" s="44" t="s">
         <v>10</v>
       </c>
@@ -2710,8 +2747,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="73"/>
-      <c r="B26" s="86"/>
+      <c r="A26" s="74"/>
+      <c r="B26" s="87"/>
       <c r="C26" s="44" t="s">
         <v>11</v>
       </c>
@@ -2726,8 +2763,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="73"/>
-      <c r="B27" s="86"/>
+      <c r="A27" s="74"/>
+      <c r="B27" s="87"/>
       <c r="C27" s="44" t="s">
         <v>13</v>
       </c>
@@ -2742,8 +2779,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="73"/>
-      <c r="B28" s="86"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="87"/>
       <c r="C28" s="44" t="s">
         <v>15</v>
       </c>
@@ -2758,10 +2795,10 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="72" t="s">
+      <c r="A29" s="73" t="s">
         <v>71</v>
       </c>
-      <c r="B29" s="75" t="s">
+      <c r="B29" s="76" t="s">
         <v>3</v>
       </c>
       <c r="C29" s="2" t="s">
@@ -2778,8 +2815,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="76"/>
+      <c r="A30" s="74"/>
+      <c r="B30" s="77"/>
       <c r="C30" t="s">
         <v>11</v>
       </c>
@@ -2794,8 +2831,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="76"/>
+      <c r="A31" s="74"/>
+      <c r="B31" s="77"/>
       <c r="C31" t="s">
         <v>13</v>
       </c>
@@ -2810,8 +2847,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="76"/>
+      <c r="A32" s="74"/>
+      <c r="B32" s="77"/>
       <c r="C32" t="s">
         <v>20</v>
       </c>
@@ -2826,8 +2863,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="73"/>
-      <c r="B33" s="76"/>
+      <c r="A33" s="74"/>
+      <c r="B33" s="77"/>
       <c r="C33" t="s">
         <v>35</v>
       </c>
@@ -2842,8 +2879,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="73"/>
-      <c r="B34" s="76"/>
+      <c r="A34" s="74"/>
+      <c r="B34" s="77"/>
       <c r="C34" t="s">
         <v>36</v>
       </c>
@@ -2858,8 +2895,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="73"/>
-      <c r="B35" s="76"/>
+      <c r="A35" s="74"/>
+      <c r="B35" s="77"/>
       <c r="C35" t="s">
         <v>15</v>
       </c>
@@ -2874,8 +2911,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="73"/>
-      <c r="B36" s="77"/>
+      <c r="A36" s="74"/>
+      <c r="B36" s="78"/>
       <c r="C36" s="5" t="s">
         <v>88</v>
       </c>
@@ -2890,8 +2927,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="73"/>
-      <c r="B37" s="78" t="s">
+      <c r="A37" s="74"/>
+      <c r="B37" s="79" t="s">
         <v>307</v>
       </c>
       <c r="C37" s="26" t="s">
@@ -2908,8 +2945,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="73"/>
-      <c r="B38" s="76"/>
+      <c r="A38" s="74"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="13" t="s">
         <v>11</v>
       </c>
@@ -2924,8 +2961,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="73"/>
-      <c r="B39" s="76"/>
+      <c r="A39" s="74"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="13" t="s">
         <v>13</v>
       </c>
@@ -2940,8 +2977,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="73"/>
-      <c r="B40" s="76"/>
+      <c r="A40" s="74"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="13" t="s">
         <v>20</v>
       </c>
@@ -2956,8 +2993,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="73"/>
-      <c r="B41" s="76"/>
+      <c r="A41" s="74"/>
+      <c r="B41" s="77"/>
       <c r="C41" s="13" t="s">
         <v>35</v>
       </c>
@@ -2972,8 +3009,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="73"/>
-      <c r="B42" s="76"/>
+      <c r="A42" s="74"/>
+      <c r="B42" s="77"/>
       <c r="C42" s="13" t="s">
         <v>36</v>
       </c>
@@ -2988,8 +3025,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="73"/>
-      <c r="B43" s="76"/>
+      <c r="A43" s="74"/>
+      <c r="B43" s="77"/>
       <c r="C43" s="13" t="s">
         <v>15</v>
       </c>
@@ -3004,8 +3041,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="73"/>
-      <c r="B44" s="76"/>
+      <c r="A44" s="74"/>
+      <c r="B44" s="77"/>
       <c r="C44" s="36" t="s">
         <v>88</v>
       </c>
@@ -3020,8 +3057,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="73"/>
-      <c r="B45" s="78" t="s">
+      <c r="A45" s="74"/>
+      <c r="B45" s="79" t="s">
         <v>203</v>
       </c>
       <c r="C45" s="4" t="s">
@@ -3038,8 +3075,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="73"/>
-      <c r="B46" s="80"/>
+      <c r="A46" s="74"/>
+      <c r="B46" s="81"/>
       <c r="C46" t="s">
         <v>21</v>
       </c>
@@ -3055,8 +3092,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="73"/>
-      <c r="B47" s="80"/>
+      <c r="A47" s="74"/>
+      <c r="B47" s="81"/>
       <c r="C47" t="s">
         <v>16</v>
       </c>
@@ -3071,8 +3108,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="73"/>
-      <c r="B48" s="80"/>
+      <c r="A48" s="74"/>
+      <c r="B48" s="81"/>
       <c r="C48" t="s">
         <v>17</v>
       </c>
@@ -3087,8 +3124,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="73"/>
-      <c r="B49" s="80"/>
+      <c r="A49" s="74"/>
+      <c r="B49" s="81"/>
       <c r="C49" t="s">
         <v>35</v>
       </c>
@@ -3103,8 +3140,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="73"/>
-      <c r="B50" s="80"/>
+      <c r="A50" s="74"/>
+      <c r="B50" s="81"/>
       <c r="C50" t="s">
         <v>36</v>
       </c>
@@ -3119,8 +3156,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="73"/>
-      <c r="B51" s="80"/>
+      <c r="A51" s="74"/>
+      <c r="B51" s="81"/>
       <c r="C51" t="s">
         <v>89</v>
       </c>
@@ -3135,8 +3172,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="73"/>
-      <c r="B52" s="80"/>
+      <c r="A52" s="74"/>
+      <c r="B52" s="81"/>
       <c r="C52" t="s">
         <v>88</v>
       </c>
@@ -3151,8 +3188,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="73"/>
-      <c r="B53" s="80"/>
+      <c r="A53" s="74"/>
+      <c r="B53" s="81"/>
       <c r="C53" t="s">
         <v>13</v>
       </c>
@@ -3167,8 +3204,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="74"/>
-      <c r="B54" s="81"/>
+      <c r="A54" s="75"/>
+      <c r="B54" s="82"/>
       <c r="C54" s="15" t="s">
         <v>15</v>
       </c>
@@ -3183,7 +3220,7 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="72" t="s">
+      <c r="A55" s="73" t="s">
         <v>72</v>
       </c>
       <c r="B55" s="11" t="s">
@@ -3203,8 +3240,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="73"/>
-      <c r="B56" s="78" t="s">
+      <c r="A56" s="74"/>
+      <c r="B56" s="79" t="s">
         <v>4</v>
       </c>
       <c r="C56" s="4" t="s">
@@ -3221,8 +3258,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="73"/>
-      <c r="B57" s="76"/>
+      <c r="A57" s="74"/>
+      <c r="B57" s="77"/>
       <c r="C57" t="s">
         <v>10</v>
       </c>
@@ -3237,8 +3274,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="73"/>
-      <c r="B58" s="76"/>
+      <c r="A58" s="74"/>
+      <c r="B58" s="77"/>
       <c r="C58" t="s">
         <v>17</v>
       </c>
@@ -3253,8 +3290,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="73"/>
-      <c r="B59" s="76"/>
+      <c r="A59" s="74"/>
+      <c r="B59" s="77"/>
       <c r="C59" t="s">
         <v>18</v>
       </c>
@@ -3269,8 +3306,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="73"/>
-      <c r="B60" s="76"/>
+      <c r="A60" s="74"/>
+      <c r="B60" s="77"/>
       <c r="C60" t="s">
         <v>13</v>
       </c>
@@ -3285,8 +3322,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="73"/>
-      <c r="B61" s="76"/>
+      <c r="A61" s="74"/>
+      <c r="B61" s="77"/>
       <c r="C61" t="s">
         <v>68</v>
       </c>
@@ -3301,8 +3338,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="73"/>
-      <c r="B62" s="77"/>
+      <c r="A62" s="74"/>
+      <c r="B62" s="78"/>
       <c r="C62" s="5" t="s">
         <v>15</v>
       </c>
@@ -3317,8 +3354,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="73"/>
-      <c r="B63" s="78" t="s">
+      <c r="A63" s="74"/>
+      <c r="B63" s="79" t="s">
         <v>5</v>
       </c>
       <c r="C63" s="4" t="s">
@@ -3335,8 +3372,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="73"/>
-      <c r="B64" s="76"/>
+      <c r="A64" s="74"/>
+      <c r="B64" s="77"/>
       <c r="C64" t="s">
         <v>10</v>
       </c>
@@ -3351,8 +3388,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="73"/>
-      <c r="B65" s="76"/>
+      <c r="A65" s="74"/>
+      <c r="B65" s="77"/>
       <c r="C65" t="s">
         <v>17</v>
       </c>
@@ -3367,8 +3404,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="73"/>
-      <c r="B66" s="76"/>
+      <c r="A66" s="74"/>
+      <c r="B66" s="77"/>
       <c r="C66" t="s">
         <v>18</v>
       </c>
@@ -3383,8 +3420,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="73"/>
-      <c r="B67" s="76"/>
+      <c r="A67" s="74"/>
+      <c r="B67" s="77"/>
       <c r="C67" t="s">
         <v>13</v>
       </c>
@@ -3399,8 +3436,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="73"/>
-      <c r="B68" s="76"/>
+      <c r="A68" s="74"/>
+      <c r="B68" s="77"/>
       <c r="C68" t="s">
         <v>68</v>
       </c>
@@ -3415,8 +3452,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="74"/>
-      <c r="B69" s="79"/>
+      <c r="A69" s="75"/>
+      <c r="B69" s="80"/>
       <c r="C69" s="15" t="s">
         <v>15</v>
       </c>
@@ -3431,7 +3468,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="72" t="s">
+      <c r="A70" s="73" t="s">
         <v>76</v>
       </c>
       <c r="B70" s="56" t="s">
@@ -3451,7 +3488,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="73"/>
+      <c r="A71" s="74"/>
       <c r="B71" s="6" t="s">
         <v>290</v>
       </c>
@@ -3469,7 +3506,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="73"/>
+      <c r="A72" s="74"/>
       <c r="B72" s="17" t="s">
         <v>79</v>
       </c>
@@ -3487,7 +3524,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="73"/>
+      <c r="A73" s="74"/>
       <c r="B73" s="17" t="s">
         <v>373</v>
       </c>
@@ -3505,7 +3542,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="74"/>
+      <c r="A74" s="75"/>
       <c r="B74" s="61" t="s">
         <v>333</v>
       </c>
@@ -3516,6 +3553,7 @@
         <v>348</v>
       </c>
       <c r="E74" s="67">
+        <f>-2.2</f>
         <v>-2.2000000000000002</v>
       </c>
       <c r="F74" s="15" t="s">
@@ -3546,7 +3584,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F146"/>
+  <dimension ref="A1:F151"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -3579,10 +3617,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="90" t="s">
+      <c r="A2" s="93" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="92" t="s">
+      <c r="B2" s="95" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3597,8 +3635,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="91"/>
-      <c r="B3" s="88"/>
+      <c r="A3" s="99"/>
+      <c r="B3" s="89"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
       </c>
@@ -3611,8 +3649,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="91"/>
-      <c r="B4" s="88"/>
+      <c r="A4" s="99"/>
+      <c r="B4" s="89"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
       </c>
@@ -3625,8 +3663,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="91"/>
-      <c r="B5" s="88"/>
+      <c r="A5" s="99"/>
+      <c r="B5" s="89"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
       </c>
@@ -3639,8 +3677,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="91"/>
-      <c r="B6" s="88"/>
+      <c r="A6" s="99"/>
+      <c r="B6" s="89"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
       </c>
@@ -3653,8 +3691,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="91"/>
-      <c r="B7" s="88"/>
+      <c r="A7" s="99"/>
+      <c r="B7" s="89"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
       </c>
@@ -3667,8 +3705,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="91"/>
-      <c r="B8" s="88"/>
+      <c r="A8" s="99"/>
+      <c r="B8" s="89"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
       </c>
@@ -3681,8 +3719,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="91"/>
-      <c r="B9" s="88"/>
+      <c r="A9" s="99"/>
+      <c r="B9" s="89"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
       </c>
@@ -3695,8 +3733,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="91"/>
-      <c r="B10" s="88"/>
+      <c r="A10" s="99"/>
+      <c r="B10" s="89"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
       </c>
@@ -3709,13 +3747,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="91"/>
-      <c r="B11" s="88"/>
+      <c r="A11" s="99"/>
+      <c r="B11" s="89"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="91"/>
-      <c r="B12" s="93" t="s">
+      <c r="A12" s="99"/>
+      <c r="B12" s="107" t="s">
         <v>366</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -3730,8 +3768,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="91"/>
-      <c r="B13" s="94"/>
+      <c r="A13" s="99"/>
+      <c r="B13" s="97"/>
       <c r="C13" s="13" t="s">
         <v>365</v>
       </c>
@@ -3744,8 +3782,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="91"/>
-      <c r="B14" s="94"/>
+      <c r="A14" s="99"/>
+      <c r="B14" s="97"/>
       <c r="C14" s="13" t="s">
         <v>382</v>
       </c>
@@ -3758,8 +3796,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="91"/>
-      <c r="B15" s="94"/>
+      <c r="A15" s="99"/>
+      <c r="B15" s="97"/>
       <c r="C15" s="13" t="s">
         <v>140</v>
       </c>
@@ -3772,8 +3810,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="91"/>
-      <c r="B16" s="94"/>
+      <c r="A16" s="99"/>
+      <c r="B16" s="97"/>
       <c r="C16" s="13" t="s">
         <v>240</v>
       </c>
@@ -3786,8 +3824,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="91"/>
-      <c r="B17" s="94"/>
+      <c r="A17" s="99"/>
+      <c r="B17" s="97"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
@@ -3800,8 +3838,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="91"/>
-      <c r="B18" s="94"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="97"/>
       <c r="C18" s="13" t="s">
         <v>142</v>
       </c>
@@ -3814,8 +3852,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="91"/>
-      <c r="B19" s="94"/>
+      <c r="A19" s="99"/>
+      <c r="B19" s="97"/>
       <c r="C19" s="13" t="s">
         <v>156</v>
       </c>
@@ -3828,8 +3866,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="91"/>
-      <c r="B20" s="94"/>
+      <c r="A20" s="99"/>
+      <c r="B20" s="97"/>
       <c r="C20" s="13" t="s">
         <v>198</v>
       </c>
@@ -3842,8 +3880,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="91"/>
-      <c r="B21" s="94"/>
+      <c r="A21" s="99"/>
+      <c r="B21" s="97"/>
       <c r="C21" s="13" t="s">
         <v>168</v>
       </c>
@@ -3856,8 +3894,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="91"/>
-      <c r="B22" s="94"/>
+      <c r="A22" s="99"/>
+      <c r="B22" s="97"/>
       <c r="C22" s="13" t="s">
         <v>190</v>
       </c>
@@ -3870,16 +3908,16 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="91"/>
-      <c r="B23" s="95"/>
+      <c r="A23" s="99"/>
+      <c r="B23" s="108"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="91"/>
-      <c r="B24" s="87" t="s">
+      <c r="A24" s="99"/>
+      <c r="B24" s="88" t="s">
         <v>264</v>
       </c>
       <c r="C24" s="13" t="s">
@@ -3894,8 +3932,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="91"/>
-      <c r="B25" s="88"/>
+      <c r="A25" s="99"/>
+      <c r="B25" s="89"/>
       <c r="C25" s="13" t="s">
         <v>108</v>
       </c>
@@ -3908,8 +3946,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="91"/>
-      <c r="B26" s="88"/>
+      <c r="A26" s="99"/>
+      <c r="B26" s="89"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
       </c>
@@ -3922,8 +3960,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="91"/>
-      <c r="B27" s="88"/>
+      <c r="A27" s="99"/>
+      <c r="B27" s="89"/>
       <c r="C27" s="13" t="s">
         <v>285</v>
       </c>
@@ -3936,8 +3974,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="91"/>
-      <c r="B28" s="88"/>
+      <c r="A28" s="99"/>
+      <c r="B28" s="89"/>
       <c r="C28" s="13" t="s">
         <v>142</v>
       </c>
@@ -3950,8 +3988,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="91"/>
-      <c r="B29" s="88"/>
+      <c r="A29" s="99"/>
+      <c r="B29" s="89"/>
       <c r="C29" s="13" t="s">
         <v>156</v>
       </c>
@@ -3964,8 +4002,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="91"/>
-      <c r="B30" s="88"/>
+      <c r="A30" s="99"/>
+      <c r="B30" s="89"/>
       <c r="C30" s="13" t="s">
         <v>198</v>
       </c>
@@ -3978,8 +4016,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="91"/>
-      <c r="B31" s="88"/>
+      <c r="A31" s="99"/>
+      <c r="B31" s="89"/>
       <c r="C31" s="13" t="s">
         <v>168</v>
       </c>
@@ -3992,8 +4030,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="91"/>
-      <c r="B32" s="88"/>
+      <c r="A32" s="99"/>
+      <c r="B32" s="89"/>
       <c r="C32" s="13" t="s">
         <v>190</v>
       </c>
@@ -4006,16 +4044,16 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="91"/>
-      <c r="B33" s="89"/>
+      <c r="A33" s="99"/>
+      <c r="B33" s="90"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
       <c r="E33" s="37"/>
       <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="91"/>
-      <c r="B34" s="86" t="s">
+      <c r="A34" s="99"/>
+      <c r="B34" s="87" t="s">
         <v>231</v>
       </c>
       <c r="C34" s="13" t="s">
@@ -4030,8 +4068,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="91"/>
-      <c r="B35" s="86"/>
+      <c r="A35" s="99"/>
+      <c r="B35" s="87"/>
       <c r="C35" s="13" t="s">
         <v>108</v>
       </c>
@@ -4044,8 +4082,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="91"/>
-      <c r="B36" s="86"/>
+      <c r="A36" s="99"/>
+      <c r="B36" s="87"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
       </c>
@@ -4058,8 +4096,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="91"/>
-      <c r="B37" s="86"/>
+      <c r="A37" s="99"/>
+      <c r="B37" s="87"/>
       <c r="C37" s="13" t="s">
         <v>272</v>
       </c>
@@ -4072,8 +4110,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="91"/>
-      <c r="B38" s="86"/>
+      <c r="A38" s="99"/>
+      <c r="B38" s="87"/>
       <c r="C38" s="13" t="s">
         <v>250</v>
       </c>
@@ -4086,8 +4124,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="91"/>
-      <c r="B39" s="86"/>
+      <c r="A39" s="99"/>
+      <c r="B39" s="87"/>
       <c r="C39" s="13" t="s">
         <v>142</v>
       </c>
@@ -4100,8 +4138,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="91"/>
-      <c r="B40" s="86"/>
+      <c r="A40" s="99"/>
+      <c r="B40" s="87"/>
       <c r="C40" s="13" t="s">
         <v>156</v>
       </c>
@@ -4114,8 +4152,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="91"/>
-      <c r="B41" s="86"/>
+      <c r="A41" s="99"/>
+      <c r="B41" s="87"/>
       <c r="C41" s="13" t="s">
         <v>198</v>
       </c>
@@ -4128,8 +4166,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="91"/>
-      <c r="B42" s="86"/>
+      <c r="A42" s="99"/>
+      <c r="B42" s="87"/>
       <c r="C42" s="13" t="s">
         <v>168</v>
       </c>
@@ -4142,8 +4180,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="91"/>
-      <c r="B43" s="86"/>
+      <c r="A43" s="99"/>
+      <c r="B43" s="87"/>
       <c r="C43" s="13" t="s">
         <v>190</v>
       </c>
@@ -4156,15 +4194,15 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="91"/>
-      <c r="B44" s="86"/>
+      <c r="A44" s="99"/>
+      <c r="B44" s="87"/>
       <c r="E44" s="33"/>
     </row>
     <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="90" t="s">
+      <c r="A45" s="93" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="99" t="s">
+      <c r="B45" s="110" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -4179,8 +4217,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="91"/>
-      <c r="B46" s="86"/>
+      <c r="A46" s="99"/>
+      <c r="B46" s="87"/>
       <c r="C46" s="13" t="s">
         <v>112</v>
       </c>
@@ -4193,8 +4231,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="91"/>
-      <c r="B47" s="86"/>
+      <c r="A47" s="99"/>
+      <c r="B47" s="87"/>
       <c r="C47" s="13" t="s">
         <v>136</v>
       </c>
@@ -4207,8 +4245,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="91"/>
-      <c r="B48" s="86"/>
+      <c r="A48" s="99"/>
+      <c r="B48" s="87"/>
       <c r="C48" s="13" t="s">
         <v>137</v>
       </c>
@@ -4221,8 +4259,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="91"/>
-      <c r="B49" s="86"/>
+      <c r="A49" s="99"/>
+      <c r="B49" s="87"/>
       <c r="C49" s="13" t="s">
         <v>142</v>
       </c>
@@ -4235,8 +4273,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="91"/>
-      <c r="B50" s="86"/>
+      <c r="A50" s="99"/>
+      <c r="B50" s="87"/>
       <c r="C50" s="13" t="s">
         <v>156</v>
       </c>
@@ -4249,8 +4287,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="91"/>
-      <c r="B51" s="86"/>
+      <c r="A51" s="99"/>
+      <c r="B51" s="87"/>
       <c r="C51" s="13" t="s">
         <v>198</v>
       </c>
@@ -4263,8 +4301,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="91"/>
-      <c r="B52" s="86"/>
+      <c r="A52" s="99"/>
+      <c r="B52" s="87"/>
       <c r="C52" s="13" t="s">
         <v>168</v>
       </c>
@@ -4277,8 +4315,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="91"/>
-      <c r="B53" s="86"/>
+      <c r="A53" s="99"/>
+      <c r="B53" s="87"/>
       <c r="C53" s="13" t="s">
         <v>190</v>
       </c>
@@ -4291,16 +4329,16 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="91"/>
-      <c r="B54" s="100"/>
+      <c r="A54" s="99"/>
+      <c r="B54" s="102"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="91"/>
-      <c r="B55" s="101" t="s">
+      <c r="A55" s="99"/>
+      <c r="B55" s="111" t="s">
         <v>307</v>
       </c>
       <c r="C55" s="44" t="s">
@@ -4315,8 +4353,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="91"/>
-      <c r="B56" s="101"/>
+      <c r="A56" s="99"/>
+      <c r="B56" s="111"/>
       <c r="C56" s="44" t="s">
         <v>112</v>
       </c>
@@ -4329,8 +4367,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="91"/>
-      <c r="B57" s="101"/>
+      <c r="A57" s="99"/>
+      <c r="B57" s="111"/>
       <c r="C57" s="44" t="s">
         <v>136</v>
       </c>
@@ -4343,8 +4381,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="91"/>
-      <c r="B58" s="101"/>
+      <c r="A58" s="99"/>
+      <c r="B58" s="111"/>
       <c r="C58" s="44" t="s">
         <v>137</v>
       </c>
@@ -4357,8 +4395,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="91"/>
-      <c r="B59" s="101"/>
+      <c r="A59" s="99"/>
+      <c r="B59" s="111"/>
       <c r="C59" s="44" t="s">
         <v>142</v>
       </c>
@@ -4371,8 +4409,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="91"/>
-      <c r="B60" s="101"/>
+      <c r="A60" s="99"/>
+      <c r="B60" s="111"/>
       <c r="C60" s="44" t="s">
         <v>156</v>
       </c>
@@ -4385,8 +4423,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="91"/>
-      <c r="B61" s="101"/>
+      <c r="A61" s="99"/>
+      <c r="B61" s="111"/>
       <c r="C61" s="44" t="s">
         <v>198</v>
       </c>
@@ -4399,8 +4437,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="91"/>
-      <c r="B62" s="101"/>
+      <c r="A62" s="99"/>
+      <c r="B62" s="111"/>
       <c r="C62" s="44" t="s">
         <v>168</v>
       </c>
@@ -4413,8 +4451,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="91"/>
-      <c r="B63" s="101"/>
+      <c r="A63" s="99"/>
+      <c r="B63" s="111"/>
       <c r="C63" s="44" t="s">
         <v>190</v>
       </c>
@@ -4427,16 +4465,16 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="91"/>
-      <c r="B64" s="102"/>
+      <c r="A64" s="99"/>
+      <c r="B64" s="112"/>
       <c r="C64" s="44"/>
       <c r="D64" s="44"/>
       <c r="E64" s="47"/>
       <c r="F64" s="44"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="91"/>
-      <c r="B65" s="97" t="s">
+      <c r="A65" s="99"/>
+      <c r="B65" s="101" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="35" t="s">
@@ -4451,8 +4489,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="91"/>
-      <c r="B66" s="86"/>
+      <c r="A66" s="99"/>
+      <c r="B66" s="87"/>
       <c r="C66" s="13" t="s">
         <v>114</v>
       </c>
@@ -4465,8 +4503,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="91"/>
-      <c r="B67" s="88"/>
+      <c r="A67" s="99"/>
+      <c r="B67" s="89"/>
       <c r="C67" s="13" t="s">
         <v>112</v>
       </c>
@@ -4479,8 +4517,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="91"/>
-      <c r="B68" s="88"/>
+      <c r="A68" s="99"/>
+      <c r="B68" s="89"/>
       <c r="C68" s="13" t="s">
         <v>108</v>
       </c>
@@ -4493,8 +4531,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="91"/>
-      <c r="B69" s="88"/>
+      <c r="A69" s="99"/>
+      <c r="B69" s="89"/>
       <c r="C69" s="13" t="s">
         <v>127</v>
       </c>
@@ -4507,8 +4545,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="91"/>
-      <c r="B70" s="88"/>
+      <c r="A70" s="99"/>
+      <c r="B70" s="89"/>
       <c r="C70" s="13" t="s">
         <v>128</v>
       </c>
@@ -4521,8 +4559,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="91"/>
-      <c r="B71" s="88"/>
+      <c r="A71" s="99"/>
+      <c r="B71" s="89"/>
       <c r="C71" s="13" t="s">
         <v>142</v>
       </c>
@@ -4535,8 +4573,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="91"/>
-      <c r="B72" s="88"/>
+      <c r="A72" s="99"/>
+      <c r="B72" s="89"/>
       <c r="C72" s="13" t="s">
         <v>156</v>
       </c>
@@ -4549,8 +4587,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="91"/>
-      <c r="B73" s="88"/>
+      <c r="A73" s="99"/>
+      <c r="B73" s="89"/>
       <c r="C73" s="13" t="s">
         <v>198</v>
       </c>
@@ -4563,8 +4601,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="91"/>
-      <c r="B74" s="88"/>
+      <c r="A74" s="99"/>
+      <c r="B74" s="89"/>
       <c r="C74" s="13" t="s">
         <v>168</v>
       </c>
@@ -4577,8 +4615,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="91"/>
-      <c r="B75" s="88"/>
+      <c r="A75" s="99"/>
+      <c r="B75" s="89"/>
       <c r="C75" s="13" t="s">
         <v>190</v>
       </c>
@@ -4591,18 +4629,18 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="96"/>
-      <c r="B76" s="98"/>
+      <c r="A76" s="100"/>
+      <c r="B76" s="109"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="90" t="s">
+      <c r="A77" s="93" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="92" t="s">
+      <c r="B77" s="95" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
@@ -4617,8 +4655,8 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="91"/>
-      <c r="B78" s="88"/>
+      <c r="A78" s="99"/>
+      <c r="B78" s="89"/>
       <c r="C78" s="13" t="s">
         <v>154</v>
       </c>
@@ -4631,13 +4669,13 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="91"/>
-      <c r="B79" s="89"/>
+      <c r="A79" s="99"/>
+      <c r="B79" s="90"/>
       <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="91"/>
-      <c r="B80" s="97" t="s">
+      <c r="A80" s="99"/>
+      <c r="B80" s="101" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="35" t="s">
@@ -4652,8 +4690,8 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="91"/>
-      <c r="B81" s="86"/>
+      <c r="A81" s="99"/>
+      <c r="B81" s="87"/>
       <c r="C81" s="13" t="s">
         <v>108</v>
       </c>
@@ -4666,8 +4704,8 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="91"/>
-      <c r="B82" s="86"/>
+      <c r="A82" s="99"/>
+      <c r="B82" s="87"/>
       <c r="C82" s="13" t="s">
         <v>123</v>
       </c>
@@ -4680,8 +4718,8 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="91"/>
-      <c r="B83" s="86"/>
+      <c r="A83" s="99"/>
+      <c r="B83" s="87"/>
       <c r="C83" s="13" t="s">
         <v>142</v>
       </c>
@@ -4694,8 +4732,8 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="91"/>
-      <c r="B84" s="86"/>
+      <c r="A84" s="99"/>
+      <c r="B84" s="87"/>
       <c r="C84" s="13" t="s">
         <v>156</v>
       </c>
@@ -4708,8 +4746,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="91"/>
-      <c r="B85" s="86"/>
+      <c r="A85" s="99"/>
+      <c r="B85" s="87"/>
       <c r="C85" s="13" t="s">
         <v>162</v>
       </c>
@@ -4722,8 +4760,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="91"/>
-      <c r="B86" s="86"/>
+      <c r="A86" s="99"/>
+      <c r="B86" s="87"/>
       <c r="C86" s="13" t="s">
         <v>198</v>
       </c>
@@ -4736,8 +4774,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="91"/>
-      <c r="B87" s="86"/>
+      <c r="A87" s="99"/>
+      <c r="B87" s="87"/>
       <c r="C87" s="13" t="s">
         <v>168</v>
       </c>
@@ -4750,8 +4788,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="91"/>
-      <c r="B88" s="86"/>
+      <c r="A88" s="99"/>
+      <c r="B88" s="87"/>
       <c r="C88" s="13" t="s">
         <v>190</v>
       </c>
@@ -4764,12 +4802,12 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="91"/>
-      <c r="B89" s="100"/>
+      <c r="A89" s="99"/>
+      <c r="B89" s="102"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="91"/>
-      <c r="B90" s="97" t="s">
+      <c r="A90" s="99"/>
+      <c r="B90" s="101" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="35" t="s">
@@ -4784,8 +4822,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="91"/>
-      <c r="B91" s="86"/>
+      <c r="A91" s="99"/>
+      <c r="B91" s="87"/>
       <c r="C91" s="13" t="s">
         <v>109</v>
       </c>
@@ -4798,8 +4836,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="91"/>
-      <c r="B92" s="86"/>
+      <c r="A92" s="99"/>
+      <c r="B92" s="87"/>
       <c r="C92" s="13" t="s">
         <v>121</v>
       </c>
@@ -4812,8 +4850,8 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="91"/>
-      <c r="B93" s="86"/>
+      <c r="A93" s="99"/>
+      <c r="B93" s="87"/>
       <c r="C93" s="13" t="s">
         <v>142</v>
       </c>
@@ -4826,8 +4864,8 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="91"/>
-      <c r="B94" s="86"/>
+      <c r="A94" s="99"/>
+      <c r="B94" s="87"/>
       <c r="C94" s="13" t="s">
         <v>156</v>
       </c>
@@ -4840,8 +4878,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="91"/>
-      <c r="B95" s="86"/>
+      <c r="A95" s="99"/>
+      <c r="B95" s="87"/>
       <c r="C95" s="13" t="s">
         <v>162</v>
       </c>
@@ -4854,8 +4892,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="91"/>
-      <c r="B96" s="86"/>
+      <c r="A96" s="99"/>
+      <c r="B96" s="87"/>
       <c r="C96" s="13" t="s">
         <v>198</v>
       </c>
@@ -4868,8 +4906,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="91"/>
-      <c r="B97" s="86"/>
+      <c r="A97" s="99"/>
+      <c r="B97" s="87"/>
       <c r="C97" s="13" t="s">
         <v>168</v>
       </c>
@@ -4882,8 +4920,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="91"/>
-      <c r="B98" s="86"/>
+      <c r="A98" s="99"/>
+      <c r="B98" s="87"/>
       <c r="C98" s="13" t="s">
         <v>190</v>
       </c>
@@ -4896,14 +4934,14 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="96"/>
-      <c r="B99" s="105"/>
+      <c r="A99" s="100"/>
+      <c r="B99" s="103"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="90" t="s">
+      <c r="A100" s="93" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="92" t="s">
+      <c r="B100" s="95" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4918,8 +4956,8 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="91"/>
-      <c r="B101" s="88"/>
+      <c r="A101" s="99"/>
+      <c r="B101" s="89"/>
       <c r="C101" s="13" t="s">
         <v>230</v>
       </c>
@@ -4932,8 +4970,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="91"/>
-      <c r="B102" s="88"/>
+      <c r="A102" s="99"/>
+      <c r="B102" s="89"/>
       <c r="C102" s="13" t="s">
         <v>151</v>
       </c>
@@ -4946,16 +4984,16 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="91"/>
-      <c r="B103" s="89"/>
+      <c r="A103" s="99"/>
+      <c r="B103" s="90"/>
       <c r="C103" s="36"/>
       <c r="D103" s="36"/>
       <c r="E103" s="37"/>
       <c r="F103" s="36"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="91"/>
-      <c r="B104" s="87" t="s">
+      <c r="A104" s="99"/>
+      <c r="B104" s="88" t="s">
         <v>294</v>
       </c>
       <c r="C104" s="13" t="s">
@@ -4970,8 +5008,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="91"/>
-      <c r="B105" s="88"/>
+      <c r="A105" s="99"/>
+      <c r="B105" s="89"/>
       <c r="C105" s="13" t="s">
         <v>299</v>
       </c>
@@ -4984,8 +5022,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="91"/>
-      <c r="B106" s="88"/>
+      <c r="A106" s="99"/>
+      <c r="B106" s="89"/>
       <c r="C106" s="13" t="s">
         <v>300</v>
       </c>
@@ -4998,13 +5036,13 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="91"/>
-      <c r="B107" s="89"/>
+      <c r="A107" s="99"/>
+      <c r="B107" s="90"/>
       <c r="E107" s="33"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="91"/>
-      <c r="B108" s="87" t="s">
+      <c r="A108" s="99"/>
+      <c r="B108" s="88" t="s">
         <v>79</v>
       </c>
       <c r="C108" s="35" t="s">
@@ -5019,8 +5057,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="91"/>
-      <c r="B109" s="106"/>
+      <c r="A109" s="99"/>
+      <c r="B109" s="91"/>
       <c r="C109" s="70" t="s">
         <v>152</v>
       </c>
@@ -5033,16 +5071,16 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="91"/>
-      <c r="B110" s="89"/>
+      <c r="A110" s="99"/>
+      <c r="B110" s="90"/>
       <c r="C110" s="36"/>
       <c r="D110" s="36"/>
       <c r="E110" s="37"/>
       <c r="F110" s="36"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="91"/>
-      <c r="B111" s="107" t="s">
+      <c r="A111" s="99"/>
+      <c r="B111" s="104" t="s">
         <v>373</v>
       </c>
       <c r="C111" s="35" t="s">
@@ -5057,8 +5095,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="91"/>
-      <c r="B112" s="108"/>
+      <c r="A112" s="99"/>
+      <c r="B112" s="105"/>
       <c r="C112" s="70" t="s">
         <v>378</v>
       </c>
@@ -5071,16 +5109,16 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="91"/>
-      <c r="B113" s="109"/>
+      <c r="A113" s="99"/>
+      <c r="B113" s="106"/>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="37"/>
       <c r="F113" s="36"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="91"/>
-      <c r="B114" s="103" t="s">
+      <c r="A114" s="99"/>
+      <c r="B114" s="96" t="s">
         <v>333</v>
       </c>
       <c r="C114" s="13" t="s">
@@ -5095,8 +5133,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="91"/>
-      <c r="B115" s="94"/>
+      <c r="A115" s="99"/>
+      <c r="B115" s="97"/>
       <c r="C115" s="13" t="s">
         <v>364</v>
       </c>
@@ -5109,18 +5147,18 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="96"/>
-      <c r="B116" s="104"/>
+      <c r="A116" s="100"/>
+      <c r="B116" s="98"/>
       <c r="C116" s="40"/>
       <c r="D116" s="40"/>
       <c r="E116" s="41"/>
       <c r="F116" s="40"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="90" t="s">
+      <c r="A117" s="93" t="s">
         <v>164</v>
       </c>
-      <c r="B117" s="92" t="s">
+      <c r="B117" s="95" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -5135,8 +5173,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="91"/>
-      <c r="B118" s="88"/>
+      <c r="A118" s="94"/>
+      <c r="B118" s="91"/>
       <c r="C118" s="13" t="s">
         <v>175</v>
       </c>
@@ -5148,16 +5186,16 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="91"/>
-      <c r="B119" s="89"/>
+      <c r="A119" s="94"/>
+      <c r="B119" s="90"/>
       <c r="C119" s="36"/>
       <c r="D119" s="36"/>
       <c r="E119" s="36"/>
       <c r="F119" s="36"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="91"/>
-      <c r="B120" s="87" t="s">
+      <c r="A120" s="94"/>
+      <c r="B120" s="88" t="s">
         <v>184</v>
       </c>
       <c r="C120" s="13" t="s">
@@ -5171,8 +5209,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="91"/>
-      <c r="B121" s="88"/>
+      <c r="A121" s="94"/>
+      <c r="B121" s="91"/>
       <c r="C121" s="13" t="s">
         <v>182</v>
       </c>
@@ -5184,8 +5222,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="91"/>
-      <c r="B122" s="88"/>
+      <c r="A122" s="94"/>
+      <c r="B122" s="91"/>
       <c r="C122" s="13" t="s">
         <v>178</v>
       </c>
@@ -5197,8 +5235,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="91"/>
-      <c r="B123" s="88"/>
+      <c r="A123" s="94"/>
+      <c r="B123" s="91"/>
       <c r="C123" s="13" t="s">
         <v>180</v>
       </c>
@@ -5210,8 +5248,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="91"/>
-      <c r="B124" s="88"/>
+      <c r="A124" s="94"/>
+      <c r="B124" s="91"/>
       <c r="C124" s="13" t="s">
         <v>183</v>
       </c>
@@ -5223,8 +5261,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="91"/>
-      <c r="B125" s="88"/>
+      <c r="A125" s="94"/>
+      <c r="B125" s="91"/>
       <c r="C125" s="13" t="s">
         <v>193</v>
       </c>
@@ -5236,12 +5274,12 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="91"/>
-      <c r="B126" s="88"/>
+      <c r="A126" s="94"/>
+      <c r="B126" s="90"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="91"/>
-      <c r="B127" s="87" t="s">
+      <c r="A127" s="94"/>
+      <c r="B127" s="88" t="s">
         <v>208</v>
       </c>
       <c r="C127" s="35" t="s">
@@ -5256,8 +5294,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="91"/>
-      <c r="B128" s="88"/>
+      <c r="A128" s="94"/>
+      <c r="B128" s="91"/>
       <c r="C128" s="13" t="s">
         <v>206</v>
       </c>
@@ -5269,8 +5307,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="91"/>
-      <c r="B129" s="88"/>
+      <c r="A129" s="94"/>
+      <c r="B129" s="91"/>
       <c r="C129" s="13" t="s">
         <v>217</v>
       </c>
@@ -5282,8 +5320,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="91"/>
-      <c r="B130" s="88"/>
+      <c r="A130" s="94"/>
+      <c r="B130" s="91"/>
       <c r="C130" s="13" t="s">
         <v>207</v>
       </c>
@@ -5295,8 +5333,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="91"/>
-      <c r="B131" s="88"/>
+      <c r="A131" s="94"/>
+      <c r="B131" s="91"/>
       <c r="C131" s="13" t="s">
         <v>302</v>
       </c>
@@ -5308,8 +5346,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="91"/>
-      <c r="B132" s="88"/>
+      <c r="A132" s="94"/>
+      <c r="B132" s="91"/>
       <c r="C132" s="44" t="s">
         <v>326</v>
       </c>
@@ -5322,8 +5360,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="91"/>
-      <c r="B133" s="88"/>
+      <c r="A133" s="94"/>
+      <c r="B133" s="91"/>
       <c r="C133" s="44" t="s">
         <v>328</v>
       </c>
@@ -5336,8 +5374,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="91"/>
-      <c r="B134" s="88"/>
+      <c r="A134" s="94"/>
+      <c r="B134" s="91"/>
       <c r="C134" s="13" t="s">
         <v>219</v>
       </c>
@@ -5349,8 +5387,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="91"/>
-      <c r="B135" s="88"/>
+      <c r="A135" s="94"/>
+      <c r="B135" s="91"/>
       <c r="C135" s="13" t="s">
         <v>223</v>
       </c>
@@ -5362,8 +5400,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="91"/>
-      <c r="B136" s="88"/>
+      <c r="A136" s="94"/>
+      <c r="B136" s="91"/>
       <c r="C136" s="13" t="s">
         <v>204</v>
       </c>
@@ -5375,8 +5413,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="91"/>
-      <c r="B137" s="88"/>
+      <c r="A137" s="94"/>
+      <c r="B137" s="91"/>
       <c r="C137" s="44" t="s">
         <v>251</v>
       </c>
@@ -5389,8 +5427,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="91"/>
-      <c r="B138" s="88"/>
+      <c r="A138" s="94"/>
+      <c r="B138" s="91"/>
       <c r="C138" s="44" t="s">
         <v>385</v>
       </c>
@@ -5403,8 +5441,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="91"/>
-      <c r="B139" s="88"/>
+      <c r="A139" s="94"/>
+      <c r="B139" s="91"/>
       <c r="C139" s="44" t="s">
         <v>367</v>
       </c>
@@ -5417,8 +5455,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="91"/>
-      <c r="B140" s="88"/>
+      <c r="A140" s="94"/>
+      <c r="B140" s="91"/>
       <c r="C140" s="44" t="s">
         <v>387</v>
       </c>
@@ -5431,16 +5469,16 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="91"/>
-      <c r="B141" s="88"/>
+      <c r="A141" s="94"/>
+      <c r="B141" s="90"/>
       <c r="C141" s="44"/>
       <c r="D141" s="44"/>
       <c r="E141" s="44"/>
       <c r="F141" s="44"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="91"/>
-      <c r="B142" s="87" t="s">
+      <c r="A142" s="94"/>
+      <c r="B142" s="88" t="s">
         <v>224</v>
       </c>
       <c r="C142" s="35" t="s">
@@ -5455,76 +5493,126 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="91"/>
-      <c r="B143" s="88"/>
-      <c r="C143" s="13" t="s">
+      <c r="A143" s="94"/>
+      <c r="B143" s="91"/>
+      <c r="C143" s="70" t="s">
         <v>304</v>
       </c>
-      <c r="D143" s="13" t="s">
+      <c r="D143" s="70" t="s">
         <v>305</v>
       </c>
-      <c r="F143" s="13" t="s">
+      <c r="E143" s="70"/>
+      <c r="F143" s="70" t="s">
         <v>306</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="91"/>
-      <c r="B144" s="88"/>
-      <c r="C144" s="13" t="s">
+      <c r="A144" s="94"/>
+      <c r="B144" s="91"/>
+      <c r="C144" s="70" t="s">
         <v>227</v>
       </c>
-      <c r="D144" s="13" t="s">
+      <c r="D144" s="70" t="s">
         <v>228</v>
       </c>
-      <c r="F144" s="13" t="s">
+      <c r="E144" s="70"/>
+      <c r="F144" s="70" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="91"/>
-      <c r="B145" s="88"/>
-      <c r="C145" s="44" t="s">
+      <c r="A145" s="94"/>
+      <c r="B145" s="91"/>
+      <c r="C145" s="72" t="s">
         <v>253</v>
       </c>
-      <c r="D145" s="44" t="s">
+      <c r="D145" s="72" t="s">
         <v>254</v>
       </c>
-      <c r="E145" s="44"/>
-      <c r="F145" s="44" t="s">
+      <c r="E145" s="72"/>
+      <c r="F145" s="72" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="91"/>
-      <c r="B146" s="88"/>
-      <c r="C146" s="44" t="s">
+      <c r="A146" s="94"/>
+      <c r="B146" s="91"/>
+      <c r="C146" s="72" t="s">
         <v>368</v>
       </c>
-      <c r="D146" s="44" t="s">
+      <c r="D146" s="72" t="s">
         <v>369</v>
       </c>
-      <c r="E146" s="44"/>
-      <c r="F146" s="44" t="s">
+      <c r="E146" s="72"/>
+      <c r="F146" s="72" t="s">
         <v>215</v>
       </c>
     </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A147" s="94"/>
+      <c r="B147" s="90"/>
+      <c r="C147" s="36"/>
+      <c r="D147" s="36"/>
+      <c r="E147" s="36"/>
+      <c r="F147" s="36"/>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A148" s="94"/>
+      <c r="B148" s="92" t="s">
+        <v>388</v>
+      </c>
+      <c r="C148" s="70" t="s">
+        <v>394</v>
+      </c>
+      <c r="D148" s="70" t="s">
+        <v>393</v>
+      </c>
+      <c r="E148" s="70"/>
+      <c r="F148" s="70" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A149" s="94"/>
+      <c r="B149" s="92"/>
+      <c r="C149" s="70" t="s">
+        <v>389</v>
+      </c>
+      <c r="D149" s="70" t="s">
+        <v>391</v>
+      </c>
+      <c r="E149" s="70"/>
+      <c r="F149" s="70" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A150" s="94"/>
+      <c r="B150" s="92"/>
+      <c r="C150" s="13" t="s">
+        <v>397</v>
+      </c>
+      <c r="D150" s="13" t="s">
+        <v>396</v>
+      </c>
+      <c r="F150" s="70" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C151" s="70" t="s">
+        <v>390</v>
+      </c>
+      <c r="D151" s="70" t="s">
+        <v>392</v>
+      </c>
+      <c r="E151" s="70"/>
+      <c r="F151" s="70" t="s">
+        <v>347</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="B114:B116"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="B120:B126"/>
-    <mergeCell ref="B142:B146"/>
-    <mergeCell ref="A117:A146"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="A77:A99"/>
-    <mergeCell ref="B80:B89"/>
-    <mergeCell ref="B90:B99"/>
-    <mergeCell ref="A100:A116"/>
-    <mergeCell ref="B100:B103"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B110"/>
-    <mergeCell ref="B111:B113"/>
+  <mergeCells count="25">
     <mergeCell ref="A2:A44"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B23"/>
@@ -5534,6 +5622,22 @@
     <mergeCell ref="B24:B33"/>
     <mergeCell ref="B45:B54"/>
     <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B114:B116"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A77:A99"/>
+    <mergeCell ref="B80:B89"/>
+    <mergeCell ref="B90:B99"/>
+    <mergeCell ref="A100:A116"/>
+    <mergeCell ref="B100:B103"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B110"/>
+    <mergeCell ref="B111:B113"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B150"/>
+    <mergeCell ref="A117:A150"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Greenfield_Patagonien_Naphta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C2DF538-87C5-4D40-9FF2-29B2E1E1C79B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF0DB87-4CAE-47E6-8CAC-2012090B5B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="677" uniqueCount="398">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="393">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1371,21 +1371,6 @@
   </si>
   <si>
     <t>calc_price</t>
-  </si>
-  <si>
-    <t>calc_maxprice_h2</t>
-  </si>
-  <si>
-    <t>Maximaler Verkaufspreis H2</t>
-  </si>
-  <si>
-    <t>€/kg_h2</t>
-  </si>
-  <si>
-    <t>calc_optprice</t>
-  </si>
-  <si>
-    <t>Verkaufspreis bei optimalem Vorverkauf</t>
   </si>
 </sst>
 </file>
@@ -3584,7 +3569,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F151"/>
+  <dimension ref="A1:F150"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="13" customWidth="1"/>
@@ -5562,24 +5547,24 @@
         <v>388</v>
       </c>
       <c r="C148" s="70" t="s">
-        <v>394</v>
+        <v>389</v>
       </c>
       <c r="D148" s="70" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="E148" s="70"/>
       <c r="F148" s="70" t="s">
-        <v>395</v>
+        <v>347</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" s="94"/>
       <c r="B149" s="92"/>
       <c r="C149" s="70" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D149" s="70" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="E149" s="70"/>
       <c r="F149" s="70" t="s">
@@ -5587,29 +5572,10 @@
       </c>
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A150" s="94"/>
-      <c r="B150" s="92"/>
-      <c r="C150" s="13" t="s">
-        <v>397</v>
-      </c>
-      <c r="D150" s="13" t="s">
-        <v>396</v>
-      </c>
-      <c r="F150" s="70" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="C151" s="70" t="s">
-        <v>390</v>
-      </c>
-      <c r="D151" s="70" t="s">
-        <v>392</v>
-      </c>
-      <c r="E151" s="70"/>
-      <c r="F151" s="70" t="s">
-        <v>347</v>
-      </c>
+      <c r="C150" s="70"/>
+      <c r="D150" s="70"/>
+      <c r="E150" s="70"/>
+      <c r="F150" s="70"/>
     </row>
   </sheetData>
   <mergeCells count="25">
@@ -5633,8 +5599,8 @@
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
     <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B150"/>
-    <mergeCell ref="A117:A150"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B127:B141"/>
     <mergeCell ref="B120:B126"/>

--- a/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
+++ b/Fischer_Tropsch/FischerTropsch_Greenfield_Patagonien_Naphta/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Fischer_Tropsch\FischerTropsch_Greenfield_Patagonien_Naphta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF0DB87-4CAE-47E6-8CAC-2012090B5B32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F256EDD-1E1C-4398-8D7F-4C54367D73A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -190,7 +190,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="671" uniqueCount="394">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1371,6 +1371,9 @@
   </si>
   <si>
     <t>calc_price</t>
+  </si>
+  <si>
+    <t>kWh_th/a</t>
   </si>
 </sst>
 </file>
@@ -1383,7 +1386,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1433,14 +1436,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFFC000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color rgb="FFFFC000"/>
       <name val="Calibri"/>
@@ -1599,9 +1594,9 @@
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="113">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
@@ -1657,29 +1652,29 @@
     <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="14" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="13" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1739,32 +1734,23 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1772,11 +1758,26 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -1787,23 +1788,11 @@
     <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -3487,7 +3476,7 @@
         <v>-1E-4</v>
       </c>
       <c r="F71" t="s">
-        <v>19</v>
+        <v>316</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
@@ -3602,10 +3591,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="93" t="s">
+      <c r="A2" s="91" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="95" t="s">
+      <c r="B2" s="93" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="26" t="s">
@@ -3620,7 +3609,7 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="99"/>
+      <c r="A3" s="92"/>
       <c r="B3" s="89"/>
       <c r="C3" s="13" t="s">
         <v>108</v>
@@ -3634,7 +3623,7 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="99"/>
+      <c r="A4" s="92"/>
       <c r="B4" s="89"/>
       <c r="C4" s="13" t="s">
         <v>84</v>
@@ -3648,7 +3637,7 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="99"/>
+      <c r="A5" s="92"/>
       <c r="B5" s="89"/>
       <c r="C5" s="13" t="s">
         <v>139</v>
@@ -3662,7 +3651,7 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="99"/>
+      <c r="A6" s="92"/>
       <c r="B6" s="89"/>
       <c r="C6" s="13" t="s">
         <v>142</v>
@@ -3676,7 +3665,7 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="99"/>
+      <c r="A7" s="92"/>
       <c r="B7" s="89"/>
       <c r="C7" s="13" t="s">
         <v>156</v>
@@ -3690,7 +3679,7 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="99"/>
+      <c r="A8" s="92"/>
       <c r="B8" s="89"/>
       <c r="C8" s="13" t="s">
         <v>198</v>
@@ -3704,7 +3693,7 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="99"/>
+      <c r="A9" s="92"/>
       <c r="B9" s="89"/>
       <c r="C9" s="13" t="s">
         <v>168</v>
@@ -3718,7 +3707,7 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="99"/>
+      <c r="A10" s="92"/>
       <c r="B10" s="89"/>
       <c r="C10" s="13" t="s">
         <v>190</v>
@@ -3732,13 +3721,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="99"/>
+      <c r="A11" s="92"/>
       <c r="B11" s="89"/>
       <c r="E11" s="33"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="99"/>
-      <c r="B12" s="107" t="s">
+      <c r="A12" s="92"/>
+      <c r="B12" s="94" t="s">
         <v>366</v>
       </c>
       <c r="C12" s="35" t="s">
@@ -3753,8 +3742,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="99"/>
-      <c r="B13" s="97"/>
+      <c r="A13" s="92"/>
+      <c r="B13" s="95"/>
       <c r="C13" s="13" t="s">
         <v>365</v>
       </c>
@@ -3767,8 +3756,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="99"/>
-      <c r="B14" s="97"/>
+      <c r="A14" s="92"/>
+      <c r="B14" s="95"/>
       <c r="C14" s="13" t="s">
         <v>382</v>
       </c>
@@ -3781,8 +3770,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="99"/>
-      <c r="B15" s="97"/>
+      <c r="A15" s="92"/>
+      <c r="B15" s="95"/>
       <c r="C15" s="13" t="s">
         <v>140</v>
       </c>
@@ -3795,8 +3784,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="99"/>
-      <c r="B16" s="97"/>
+      <c r="A16" s="92"/>
+      <c r="B16" s="95"/>
       <c r="C16" s="13" t="s">
         <v>240</v>
       </c>
@@ -3809,8 +3798,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="99"/>
-      <c r="B17" s="97"/>
+      <c r="A17" s="92"/>
+      <c r="B17" s="95"/>
       <c r="C17" s="13" t="s">
         <v>84</v>
       </c>
@@ -3823,8 +3812,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="99"/>
-      <c r="B18" s="97"/>
+      <c r="A18" s="92"/>
+      <c r="B18" s="95"/>
       <c r="C18" s="13" t="s">
         <v>142</v>
       </c>
@@ -3837,8 +3826,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="99"/>
-      <c r="B19" s="97"/>
+      <c r="A19" s="92"/>
+      <c r="B19" s="95"/>
       <c r="C19" s="13" t="s">
         <v>156</v>
       </c>
@@ -3851,8 +3840,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="99"/>
-      <c r="B20" s="97"/>
+      <c r="A20" s="92"/>
+      <c r="B20" s="95"/>
       <c r="C20" s="13" t="s">
         <v>198</v>
       </c>
@@ -3865,8 +3854,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="99"/>
-      <c r="B21" s="97"/>
+      <c r="A21" s="92"/>
+      <c r="B21" s="95"/>
       <c r="C21" s="13" t="s">
         <v>168</v>
       </c>
@@ -3879,8 +3868,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="99"/>
-      <c r="B22" s="97"/>
+      <c r="A22" s="92"/>
+      <c r="B22" s="95"/>
       <c r="C22" s="13" t="s">
         <v>190</v>
       </c>
@@ -3893,15 +3882,15 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="99"/>
-      <c r="B23" s="108"/>
+      <c r="A23" s="92"/>
+      <c r="B23" s="96"/>
       <c r="C23" s="36"/>
       <c r="D23" s="36"/>
       <c r="E23" s="37"/>
       <c r="F23" s="36"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="99"/>
+      <c r="A24" s="92"/>
       <c r="B24" s="88" t="s">
         <v>264</v>
       </c>
@@ -3917,7 +3906,7 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="99"/>
+      <c r="A25" s="92"/>
       <c r="B25" s="89"/>
       <c r="C25" s="13" t="s">
         <v>108</v>
@@ -3931,7 +3920,7 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="99"/>
+      <c r="A26" s="92"/>
       <c r="B26" s="89"/>
       <c r="C26" s="13" t="s">
         <v>84</v>
@@ -3945,7 +3934,7 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="99"/>
+      <c r="A27" s="92"/>
       <c r="B27" s="89"/>
       <c r="C27" s="13" t="s">
         <v>285</v>
@@ -3959,7 +3948,7 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="99"/>
+      <c r="A28" s="92"/>
       <c r="B28" s="89"/>
       <c r="C28" s="13" t="s">
         <v>142</v>
@@ -3973,7 +3962,7 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="99"/>
+      <c r="A29" s="92"/>
       <c r="B29" s="89"/>
       <c r="C29" s="13" t="s">
         <v>156</v>
@@ -3987,7 +3976,7 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="99"/>
+      <c r="A30" s="92"/>
       <c r="B30" s="89"/>
       <c r="C30" s="13" t="s">
         <v>198</v>
@@ -4001,7 +3990,7 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="99"/>
+      <c r="A31" s="92"/>
       <c r="B31" s="89"/>
       <c r="C31" s="13" t="s">
         <v>168</v>
@@ -4015,7 +4004,7 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="99"/>
+      <c r="A32" s="92"/>
       <c r="B32" s="89"/>
       <c r="C32" s="13" t="s">
         <v>190</v>
@@ -4029,7 +4018,7 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="99"/>
+      <c r="A33" s="92"/>
       <c r="B33" s="90"/>
       <c r="C33" s="36"/>
       <c r="D33" s="36"/>
@@ -4037,7 +4026,7 @@
       <c r="F33" s="36"/>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="99"/>
+      <c r="A34" s="92"/>
       <c r="B34" s="87" t="s">
         <v>231</v>
       </c>
@@ -4053,7 +4042,7 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="99"/>
+      <c r="A35" s="92"/>
       <c r="B35" s="87"/>
       <c r="C35" s="13" t="s">
         <v>108</v>
@@ -4067,7 +4056,7 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="99"/>
+      <c r="A36" s="92"/>
       <c r="B36" s="87"/>
       <c r="C36" s="13" t="s">
         <v>84</v>
@@ -4081,7 +4070,7 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="99"/>
+      <c r="A37" s="92"/>
       <c r="B37" s="87"/>
       <c r="C37" s="13" t="s">
         <v>272</v>
@@ -4095,7 +4084,7 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="99"/>
+      <c r="A38" s="92"/>
       <c r="B38" s="87"/>
       <c r="C38" s="13" t="s">
         <v>250</v>
@@ -4109,7 +4098,7 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="99"/>
+      <c r="A39" s="92"/>
       <c r="B39" s="87"/>
       <c r="C39" s="13" t="s">
         <v>142</v>
@@ -4123,7 +4112,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="99"/>
+      <c r="A40" s="92"/>
       <c r="B40" s="87"/>
       <c r="C40" s="13" t="s">
         <v>156</v>
@@ -4137,7 +4126,7 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="99"/>
+      <c r="A41" s="92"/>
       <c r="B41" s="87"/>
       <c r="C41" s="13" t="s">
         <v>198</v>
@@ -4151,7 +4140,7 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="99"/>
+      <c r="A42" s="92"/>
       <c r="B42" s="87"/>
       <c r="C42" s="13" t="s">
         <v>168</v>
@@ -4165,7 +4154,7 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="99"/>
+      <c r="A43" s="92"/>
       <c r="B43" s="87"/>
       <c r="C43" s="13" t="s">
         <v>190</v>
@@ -4179,15 +4168,15 @@
       </c>
     </row>
     <row r="44" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A44" s="99"/>
+      <c r="A44" s="92"/>
       <c r="B44" s="87"/>
       <c r="E44" s="33"/>
     </row>
     <row r="45" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="93" t="s">
+      <c r="A45" s="91" t="s">
         <v>71</v>
       </c>
-      <c r="B45" s="110" t="s">
+      <c r="B45" s="100" t="s">
         <v>3</v>
       </c>
       <c r="C45" s="26" t="s">
@@ -4202,7 +4191,7 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="99"/>
+      <c r="A46" s="92"/>
       <c r="B46" s="87"/>
       <c r="C46" s="13" t="s">
         <v>112</v>
@@ -4216,7 +4205,7 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="99"/>
+      <c r="A47" s="92"/>
       <c r="B47" s="87"/>
       <c r="C47" s="13" t="s">
         <v>136</v>
@@ -4230,7 +4219,7 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="99"/>
+      <c r="A48" s="92"/>
       <c r="B48" s="87"/>
       <c r="C48" s="13" t="s">
         <v>137</v>
@@ -4244,7 +4233,7 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="99"/>
+      <c r="A49" s="92"/>
       <c r="B49" s="87"/>
       <c r="C49" s="13" t="s">
         <v>142</v>
@@ -4258,7 +4247,7 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="99"/>
+      <c r="A50" s="92"/>
       <c r="B50" s="87"/>
       <c r="C50" s="13" t="s">
         <v>156</v>
@@ -4272,7 +4261,7 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="99"/>
+      <c r="A51" s="92"/>
       <c r="B51" s="87"/>
       <c r="C51" s="13" t="s">
         <v>198</v>
@@ -4286,7 +4275,7 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="99"/>
+      <c r="A52" s="92"/>
       <c r="B52" s="87"/>
       <c r="C52" s="13" t="s">
         <v>168</v>
@@ -4300,7 +4289,7 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="99"/>
+      <c r="A53" s="92"/>
       <c r="B53" s="87"/>
       <c r="C53" s="13" t="s">
         <v>190</v>
@@ -4314,152 +4303,149 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="99"/>
-      <c r="B54" s="102"/>
+      <c r="A54" s="92"/>
+      <c r="B54" s="101"/>
       <c r="C54" s="36"/>
       <c r="D54" s="36"/>
       <c r="E54" s="37"/>
       <c r="F54" s="36"/>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="99"/>
-      <c r="B55" s="111" t="s">
+      <c r="A55" s="92"/>
+      <c r="B55" s="87" t="s">
         <v>307</v>
       </c>
-      <c r="C55" s="44" t="s">
+      <c r="C55" s="13" t="s">
         <v>114</v>
       </c>
-      <c r="D55" s="44" t="s">
+      <c r="D55" s="13" t="s">
         <v>317</v>
       </c>
-      <c r="E55" s="46"/>
-      <c r="F55" s="44" t="s">
+      <c r="E55" s="31"/>
+      <c r="F55" s="13" t="s">
         <v>330</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="99"/>
-      <c r="B56" s="111"/>
-      <c r="C56" s="44" t="s">
+      <c r="A56" s="92"/>
+      <c r="B56" s="87"/>
+      <c r="C56" s="13" t="s">
         <v>112</v>
       </c>
-      <c r="D56" s="44" t="s">
+      <c r="D56" s="13" t="s">
         <v>318</v>
       </c>
-      <c r="E56" s="47"/>
-      <c r="F56" s="44" t="s">
+      <c r="E56" s="33"/>
+      <c r="F56" s="13" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="99"/>
-      <c r="B57" s="111"/>
-      <c r="C57" s="44" t="s">
+      <c r="A57" s="92"/>
+      <c r="B57" s="87"/>
+      <c r="C57" s="13" t="s">
         <v>136</v>
       </c>
-      <c r="D57" s="44" t="s">
+      <c r="D57" s="13" t="s">
         <v>319</v>
       </c>
-      <c r="E57" s="48"/>
-      <c r="F57" s="59" t="s">
-        <v>133</v>
+      <c r="E57" s="34"/>
+      <c r="F57" s="13" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="99"/>
-      <c r="B58" s="111"/>
-      <c r="C58" s="44" t="s">
+      <c r="A58" s="92"/>
+      <c r="B58" s="87"/>
+      <c r="C58" s="13" t="s">
         <v>137</v>
       </c>
-      <c r="D58" s="44" t="s">
+      <c r="D58" s="13" t="s">
         <v>320</v>
       </c>
-      <c r="E58" s="47"/>
-      <c r="F58" s="59" t="s">
-        <v>133</v>
+      <c r="E58" s="33"/>
+      <c r="F58" s="13" t="s">
+        <v>393</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="99"/>
-      <c r="B59" s="111"/>
-      <c r="C59" s="44" t="s">
+      <c r="A59" s="92"/>
+      <c r="B59" s="87"/>
+      <c r="C59" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="D59" s="44" t="s">
+      <c r="D59" s="13" t="s">
         <v>321</v>
       </c>
-      <c r="E59" s="47"/>
-      <c r="F59" s="59" t="s">
+      <c r="E59" s="33"/>
+      <c r="F59" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="99"/>
-      <c r="B60" s="111"/>
-      <c r="C60" s="44" t="s">
+      <c r="A60" s="92"/>
+      <c r="B60" s="87"/>
+      <c r="C60" s="13" t="s">
         <v>156</v>
       </c>
-      <c r="D60" s="44" t="s">
+      <c r="D60" s="13" t="s">
         <v>322</v>
       </c>
-      <c r="E60" s="47"/>
-      <c r="F60" s="59" t="s">
+      <c r="E60" s="33"/>
+      <c r="F60" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="99"/>
-      <c r="B61" s="111"/>
-      <c r="C61" s="44" t="s">
+      <c r="A61" s="92"/>
+      <c r="B61" s="87"/>
+      <c r="C61" s="13" t="s">
         <v>198</v>
       </c>
-      <c r="D61" s="44" t="s">
+      <c r="D61" s="13" t="s">
         <v>323</v>
       </c>
-      <c r="E61" s="47"/>
-      <c r="F61" s="59" t="s">
+      <c r="E61" s="33"/>
+      <c r="F61" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="99"/>
-      <c r="B62" s="111"/>
-      <c r="C62" s="44" t="s">
+      <c r="A62" s="92"/>
+      <c r="B62" s="87"/>
+      <c r="C62" s="13" t="s">
         <v>168</v>
       </c>
-      <c r="D62" s="44" t="s">
+      <c r="D62" s="13" t="s">
         <v>324</v>
       </c>
-      <c r="E62" s="47"/>
-      <c r="F62" s="59" t="s">
+      <c r="E62" s="33"/>
+      <c r="F62" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="99"/>
-      <c r="B63" s="111"/>
-      <c r="C63" s="44" t="s">
+      <c r="A63" s="92"/>
+      <c r="B63" s="87"/>
+      <c r="C63" s="13" t="s">
         <v>190</v>
       </c>
-      <c r="D63" s="44" t="s">
+      <c r="D63" s="13" t="s">
         <v>325</v>
       </c>
-      <c r="E63" s="47"/>
-      <c r="F63" s="59" t="s">
+      <c r="E63" s="33"/>
+      <c r="F63" s="13" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="99"/>
-      <c r="B64" s="112"/>
-      <c r="C64" s="44"/>
-      <c r="D64" s="44"/>
-      <c r="E64" s="47"/>
-      <c r="F64" s="44"/>
+      <c r="A64" s="92"/>
+      <c r="B64" s="101"/>
+      <c r="E64" s="33"/>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="99"/>
-      <c r="B65" s="101" t="s">
+      <c r="A65" s="92"/>
+      <c r="B65" s="98" t="s">
         <v>6</v>
       </c>
       <c r="C65" s="35" t="s">
@@ -4474,7 +4460,7 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="99"/>
+      <c r="A66" s="92"/>
       <c r="B66" s="87"/>
       <c r="C66" s="13" t="s">
         <v>114</v>
@@ -4488,7 +4474,7 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="99"/>
+      <c r="A67" s="92"/>
       <c r="B67" s="89"/>
       <c r="C67" s="13" t="s">
         <v>112</v>
@@ -4502,7 +4488,7 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="99"/>
+      <c r="A68" s="92"/>
       <c r="B68" s="89"/>
       <c r="C68" s="13" t="s">
         <v>108</v>
@@ -4516,7 +4502,7 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="99"/>
+      <c r="A69" s="92"/>
       <c r="B69" s="89"/>
       <c r="C69" s="13" t="s">
         <v>127</v>
@@ -4530,7 +4516,7 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="99"/>
+      <c r="A70" s="92"/>
       <c r="B70" s="89"/>
       <c r="C70" s="13" t="s">
         <v>128</v>
@@ -4544,7 +4530,7 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="99"/>
+      <c r="A71" s="92"/>
       <c r="B71" s="89"/>
       <c r="C71" s="13" t="s">
         <v>142</v>
@@ -4558,7 +4544,7 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="99"/>
+      <c r="A72" s="92"/>
       <c r="B72" s="89"/>
       <c r="C72" s="13" t="s">
         <v>156</v>
@@ -4572,7 +4558,7 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="99"/>
+      <c r="A73" s="92"/>
       <c r="B73" s="89"/>
       <c r="C73" s="13" t="s">
         <v>198</v>
@@ -4586,7 +4572,7 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="99"/>
+      <c r="A74" s="92"/>
       <c r="B74" s="89"/>
       <c r="C74" s="13" t="s">
         <v>168</v>
@@ -4600,7 +4586,7 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="99"/>
+      <c r="A75" s="92"/>
       <c r="B75" s="89"/>
       <c r="C75" s="13" t="s">
         <v>190</v>
@@ -4614,18 +4600,18 @@
       </c>
     </row>
     <row r="76" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A76" s="100"/>
-      <c r="B76" s="109"/>
+      <c r="A76" s="97"/>
+      <c r="B76" s="99"/>
       <c r="C76" s="40"/>
       <c r="D76" s="40"/>
       <c r="E76" s="41"/>
       <c r="F76" s="40"/>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A77" s="93" t="s">
+      <c r="A77" s="91" t="s">
         <v>72</v>
       </c>
-      <c r="B77" s="95" t="s">
+      <c r="B77" s="93" t="s">
         <v>73</v>
       </c>
       <c r="C77" s="26" t="s">
@@ -4640,7 +4626,7 @@
       </c>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="99"/>
+      <c r="A78" s="92"/>
       <c r="B78" s="89"/>
       <c r="C78" s="13" t="s">
         <v>154</v>
@@ -4654,13 +4640,13 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="99"/>
+      <c r="A79" s="92"/>
       <c r="B79" s="90"/>
       <c r="E79" s="31"/>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="99"/>
-      <c r="B80" s="101" t="s">
+      <c r="A80" s="92"/>
+      <c r="B80" s="98" t="s">
         <v>4</v>
       </c>
       <c r="C80" s="35" t="s">
@@ -4675,7 +4661,7 @@
       </c>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="99"/>
+      <c r="A81" s="92"/>
       <c r="B81" s="87"/>
       <c r="C81" s="13" t="s">
         <v>108</v>
@@ -4689,7 +4675,7 @@
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="99"/>
+      <c r="A82" s="92"/>
       <c r="B82" s="87"/>
       <c r="C82" s="13" t="s">
         <v>123</v>
@@ -4703,7 +4689,7 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="99"/>
+      <c r="A83" s="92"/>
       <c r="B83" s="87"/>
       <c r="C83" s="13" t="s">
         <v>142</v>
@@ -4717,7 +4703,7 @@
       </c>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="99"/>
+      <c r="A84" s="92"/>
       <c r="B84" s="87"/>
       <c r="C84" s="13" t="s">
         <v>156</v>
@@ -4731,7 +4717,7 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="99"/>
+      <c r="A85" s="92"/>
       <c r="B85" s="87"/>
       <c r="C85" s="13" t="s">
         <v>162</v>
@@ -4745,7 +4731,7 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="99"/>
+      <c r="A86" s="92"/>
       <c r="B86" s="87"/>
       <c r="C86" s="13" t="s">
         <v>198</v>
@@ -4759,7 +4745,7 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="99"/>
+      <c r="A87" s="92"/>
       <c r="B87" s="87"/>
       <c r="C87" s="13" t="s">
         <v>168</v>
@@ -4773,7 +4759,7 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="99"/>
+      <c r="A88" s="92"/>
       <c r="B88" s="87"/>
       <c r="C88" s="13" t="s">
         <v>190</v>
@@ -4787,12 +4773,12 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="99"/>
-      <c r="B89" s="102"/>
+      <c r="A89" s="92"/>
+      <c r="B89" s="101"/>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="99"/>
-      <c r="B90" s="101" t="s">
+      <c r="A90" s="92"/>
+      <c r="B90" s="98" t="s">
         <v>5</v>
       </c>
       <c r="C90" s="35" t="s">
@@ -4807,7 +4793,7 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="99"/>
+      <c r="A91" s="92"/>
       <c r="B91" s="87"/>
       <c r="C91" s="13" t="s">
         <v>109</v>
@@ -4821,7 +4807,7 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="99"/>
+      <c r="A92" s="92"/>
       <c r="B92" s="87"/>
       <c r="C92" s="13" t="s">
         <v>121</v>
@@ -4835,7 +4821,7 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="99"/>
+      <c r="A93" s="92"/>
       <c r="B93" s="87"/>
       <c r="C93" s="13" t="s">
         <v>142</v>
@@ -4849,7 +4835,7 @@
       </c>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="99"/>
+      <c r="A94" s="92"/>
       <c r="B94" s="87"/>
       <c r="C94" s="13" t="s">
         <v>156</v>
@@ -4863,7 +4849,7 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="99"/>
+      <c r="A95" s="92"/>
       <c r="B95" s="87"/>
       <c r="C95" s="13" t="s">
         <v>162</v>
@@ -4877,7 +4863,7 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="99"/>
+      <c r="A96" s="92"/>
       <c r="B96" s="87"/>
       <c r="C96" s="13" t="s">
         <v>198</v>
@@ -4891,7 +4877,7 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="99"/>
+      <c r="A97" s="92"/>
       <c r="B97" s="87"/>
       <c r="C97" s="13" t="s">
         <v>168</v>
@@ -4905,7 +4891,7 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="99"/>
+      <c r="A98" s="92"/>
       <c r="B98" s="87"/>
       <c r="C98" s="13" t="s">
         <v>190</v>
@@ -4919,14 +4905,14 @@
       </c>
     </row>
     <row r="99" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="100"/>
-      <c r="B99" s="103"/>
+      <c r="A99" s="97"/>
+      <c r="B99" s="104"/>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="93" t="s">
+      <c r="A100" s="91" t="s">
         <v>76</v>
       </c>
-      <c r="B100" s="95" t="s">
+      <c r="B100" s="93" t="s">
         <v>73</v>
       </c>
       <c r="C100" s="26" t="s">
@@ -4941,7 +4927,7 @@
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="99"/>
+      <c r="A101" s="92"/>
       <c r="B101" s="89"/>
       <c r="C101" s="13" t="s">
         <v>230</v>
@@ -4955,7 +4941,7 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="99"/>
+      <c r="A102" s="92"/>
       <c r="B102" s="89"/>
       <c r="C102" s="13" t="s">
         <v>151</v>
@@ -4969,7 +4955,7 @@
       </c>
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A103" s="99"/>
+      <c r="A103" s="92"/>
       <c r="B103" s="90"/>
       <c r="C103" s="36"/>
       <c r="D103" s="36"/>
@@ -4977,7 +4963,7 @@
       <c r="F103" s="36"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="99"/>
+      <c r="A104" s="92"/>
       <c r="B104" s="88" t="s">
         <v>294</v>
       </c>
@@ -4993,7 +4979,7 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="99"/>
+      <c r="A105" s="92"/>
       <c r="B105" s="89"/>
       <c r="C105" s="13" t="s">
         <v>299</v>
@@ -5007,7 +4993,7 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="99"/>
+      <c r="A106" s="92"/>
       <c r="B106" s="89"/>
       <c r="C106" s="13" t="s">
         <v>300</v>
@@ -5021,12 +5007,12 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="99"/>
+      <c r="A107" s="92"/>
       <c r="B107" s="90"/>
       <c r="E107" s="33"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="99"/>
+      <c r="A108" s="92"/>
       <c r="B108" s="88" t="s">
         <v>79</v>
       </c>
@@ -5042,8 +5028,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="99"/>
-      <c r="B109" s="91"/>
+      <c r="A109" s="92"/>
+      <c r="B109" s="105"/>
       <c r="C109" s="70" t="s">
         <v>152</v>
       </c>
@@ -5056,7 +5042,7 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="99"/>
+      <c r="A110" s="92"/>
       <c r="B110" s="90"/>
       <c r="C110" s="36"/>
       <c r="D110" s="36"/>
@@ -5064,8 +5050,8 @@
       <c r="F110" s="36"/>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="99"/>
-      <c r="B111" s="104" t="s">
+      <c r="A111" s="92"/>
+      <c r="B111" s="106" t="s">
         <v>373</v>
       </c>
       <c r="C111" s="35" t="s">
@@ -5080,8 +5066,8 @@
       </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="99"/>
-      <c r="B112" s="105"/>
+      <c r="A112" s="92"/>
+      <c r="B112" s="107"/>
       <c r="C112" s="70" t="s">
         <v>378</v>
       </c>
@@ -5094,16 +5080,16 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="99"/>
-      <c r="B113" s="106"/>
+      <c r="A113" s="92"/>
+      <c r="B113" s="108"/>
       <c r="C113" s="36"/>
       <c r="D113" s="36"/>
       <c r="E113" s="37"/>
       <c r="F113" s="36"/>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="99"/>
-      <c r="B114" s="96" t="s">
+      <c r="A114" s="92"/>
+      <c r="B114" s="102" t="s">
         <v>333</v>
       </c>
       <c r="C114" s="13" t="s">
@@ -5118,8 +5104,8 @@
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="99"/>
-      <c r="B115" s="97"/>
+      <c r="A115" s="92"/>
+      <c r="B115" s="95"/>
       <c r="C115" s="13" t="s">
         <v>364</v>
       </c>
@@ -5132,18 +5118,18 @@
       </c>
     </row>
     <row r="116" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="100"/>
-      <c r="B116" s="98"/>
+      <c r="A116" s="97"/>
+      <c r="B116" s="103"/>
       <c r="C116" s="40"/>
       <c r="D116" s="40"/>
       <c r="E116" s="41"/>
       <c r="F116" s="40"/>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A117" s="93" t="s">
+      <c r="A117" s="91" t="s">
         <v>164</v>
       </c>
-      <c r="B117" s="95" t="s">
+      <c r="B117" s="93" t="s">
         <v>13</v>
       </c>
       <c r="C117" s="26" t="s">
@@ -5158,8 +5144,8 @@
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="94"/>
-      <c r="B118" s="91"/>
+      <c r="A118" s="110"/>
+      <c r="B118" s="105"/>
       <c r="C118" s="13" t="s">
         <v>175</v>
       </c>
@@ -5171,7 +5157,7 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="94"/>
+      <c r="A119" s="110"/>
       <c r="B119" s="90"/>
       <c r="C119" s="36"/>
       <c r="D119" s="36"/>
@@ -5179,7 +5165,7 @@
       <c r="F119" s="36"/>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="94"/>
+      <c r="A120" s="110"/>
       <c r="B120" s="88" t="s">
         <v>184</v>
       </c>
@@ -5194,8 +5180,8 @@
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="94"/>
-      <c r="B121" s="91"/>
+      <c r="A121" s="110"/>
+      <c r="B121" s="105"/>
       <c r="C121" s="13" t="s">
         <v>182</v>
       </c>
@@ -5207,8 +5193,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="94"/>
-      <c r="B122" s="91"/>
+      <c r="A122" s="110"/>
+      <c r="B122" s="105"/>
       <c r="C122" s="13" t="s">
         <v>178</v>
       </c>
@@ -5220,8 +5206,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="94"/>
-      <c r="B123" s="91"/>
+      <c r="A123" s="110"/>
+      <c r="B123" s="105"/>
       <c r="C123" s="13" t="s">
         <v>180</v>
       </c>
@@ -5233,8 +5219,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="94"/>
-      <c r="B124" s="91"/>
+      <c r="A124" s="110"/>
+      <c r="B124" s="105"/>
       <c r="C124" s="13" t="s">
         <v>183</v>
       </c>
@@ -5246,8 +5232,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="94"/>
-      <c r="B125" s="91"/>
+      <c r="A125" s="110"/>
+      <c r="B125" s="105"/>
       <c r="C125" s="13" t="s">
         <v>193</v>
       </c>
@@ -5259,11 +5245,11 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="94"/>
+      <c r="A126" s="110"/>
       <c r="B126" s="90"/>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="94"/>
+      <c r="A127" s="110"/>
       <c r="B127" s="88" t="s">
         <v>208</v>
       </c>
@@ -5279,8 +5265,8 @@
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="94"/>
-      <c r="B128" s="91"/>
+      <c r="A128" s="110"/>
+      <c r="B128" s="105"/>
       <c r="C128" s="13" t="s">
         <v>206</v>
       </c>
@@ -5292,8 +5278,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="94"/>
-      <c r="B129" s="91"/>
+      <c r="A129" s="110"/>
+      <c r="B129" s="105"/>
       <c r="C129" s="13" t="s">
         <v>217</v>
       </c>
@@ -5305,8 +5291,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="94"/>
-      <c r="B130" s="91"/>
+      <c r="A130" s="110"/>
+      <c r="B130" s="105"/>
       <c r="C130" s="13" t="s">
         <v>207</v>
       </c>
@@ -5318,8 +5304,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="94"/>
-      <c r="B131" s="91"/>
+      <c r="A131" s="110"/>
+      <c r="B131" s="105"/>
       <c r="C131" s="13" t="s">
         <v>302</v>
       </c>
@@ -5331,8 +5317,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="94"/>
-      <c r="B132" s="91"/>
+      <c r="A132" s="110"/>
+      <c r="B132" s="105"/>
       <c r="C132" s="44" t="s">
         <v>326</v>
       </c>
@@ -5345,8 +5331,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="94"/>
-      <c r="B133" s="91"/>
+      <c r="A133" s="110"/>
+      <c r="B133" s="105"/>
       <c r="C133" s="44" t="s">
         <v>328</v>
       </c>
@@ -5359,8 +5345,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="94"/>
-      <c r="B134" s="91"/>
+      <c r="A134" s="110"/>
+      <c r="B134" s="105"/>
       <c r="C134" s="13" t="s">
         <v>219</v>
       </c>
@@ -5372,8 +5358,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="94"/>
-      <c r="B135" s="91"/>
+      <c r="A135" s="110"/>
+      <c r="B135" s="105"/>
       <c r="C135" s="13" t="s">
         <v>223</v>
       </c>
@@ -5385,8 +5371,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="94"/>
-      <c r="B136" s="91"/>
+      <c r="A136" s="110"/>
+      <c r="B136" s="105"/>
       <c r="C136" s="13" t="s">
         <v>204</v>
       </c>
@@ -5398,8 +5384,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="94"/>
-      <c r="B137" s="91"/>
+      <c r="A137" s="110"/>
+      <c r="B137" s="105"/>
       <c r="C137" s="44" t="s">
         <v>251</v>
       </c>
@@ -5412,8 +5398,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="94"/>
-      <c r="B138" s="91"/>
+      <c r="A138" s="110"/>
+      <c r="B138" s="105"/>
       <c r="C138" s="44" t="s">
         <v>385</v>
       </c>
@@ -5426,8 +5412,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="94"/>
-      <c r="B139" s="91"/>
+      <c r="A139" s="110"/>
+      <c r="B139" s="105"/>
       <c r="C139" s="44" t="s">
         <v>367</v>
       </c>
@@ -5440,8 +5426,8 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="94"/>
-      <c r="B140" s="91"/>
+      <c r="A140" s="110"/>
+      <c r="B140" s="105"/>
       <c r="C140" s="44" t="s">
         <v>387</v>
       </c>
@@ -5454,7 +5440,7 @@
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="94"/>
+      <c r="A141" s="110"/>
       <c r="B141" s="90"/>
       <c r="C141" s="44"/>
       <c r="D141" s="44"/>
@@ -5462,7 +5448,7 @@
       <c r="F141" s="44"/>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="94"/>
+      <c r="A142" s="110"/>
       <c r="B142" s="88" t="s">
         <v>224</v>
       </c>
@@ -5478,8 +5464,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="94"/>
-      <c r="B143" s="91"/>
+      <c r="A143" s="110"/>
+      <c r="B143" s="105"/>
       <c r="C143" s="70" t="s">
         <v>304</v>
       </c>
@@ -5492,8 +5478,8 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="94"/>
-      <c r="B144" s="91"/>
+      <c r="A144" s="110"/>
+      <c r="B144" s="105"/>
       <c r="C144" s="70" t="s">
         <v>227</v>
       </c>
@@ -5506,8 +5492,8 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="94"/>
-      <c r="B145" s="91"/>
+      <c r="A145" s="110"/>
+      <c r="B145" s="105"/>
       <c r="C145" s="72" t="s">
         <v>253</v>
       </c>
@@ -5520,8 +5506,8 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="94"/>
-      <c r="B146" s="91"/>
+      <c r="A146" s="110"/>
+      <c r="B146" s="105"/>
       <c r="C146" s="72" t="s">
         <v>368</v>
       </c>
@@ -5534,7 +5520,7 @@
       </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="94"/>
+      <c r="A147" s="110"/>
       <c r="B147" s="90"/>
       <c r="C147" s="36"/>
       <c r="D147" s="36"/>
@@ -5542,8 +5528,8 @@
       <c r="F147" s="36"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="94"/>
-      <c r="B148" s="92" t="s">
+      <c r="A148" s="110"/>
+      <c r="B148" s="109" t="s">
         <v>388</v>
       </c>
       <c r="C148" s="70" t="s">
@@ -5558,8 +5544,8 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="94"/>
-      <c r="B149" s="92"/>
+      <c r="A149" s="110"/>
+      <c r="B149" s="109"/>
       <c r="C149" s="70" t="s">
         <v>390</v>
       </c>
@@ -5579,15 +5565,12 @@
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="A2:A44"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="B34:B44"/>
-    <mergeCell ref="A45:A76"/>
-    <mergeCell ref="B65:B76"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B45:B54"/>
-    <mergeCell ref="B55:B64"/>
+    <mergeCell ref="B142:B147"/>
+    <mergeCell ref="B148:B149"/>
+    <mergeCell ref="A117:A149"/>
+    <mergeCell ref="B117:B119"/>
+    <mergeCell ref="B127:B141"/>
+    <mergeCell ref="B120:B126"/>
     <mergeCell ref="B114:B116"/>
     <mergeCell ref="B77:B79"/>
     <mergeCell ref="A77:A99"/>
@@ -5598,12 +5581,15 @@
     <mergeCell ref="B104:B107"/>
     <mergeCell ref="B108:B110"/>
     <mergeCell ref="B111:B113"/>
-    <mergeCell ref="B142:B147"/>
-    <mergeCell ref="B148:B149"/>
-    <mergeCell ref="A117:A149"/>
-    <mergeCell ref="B117:B119"/>
-    <mergeCell ref="B127:B141"/>
-    <mergeCell ref="B120:B126"/>
+    <mergeCell ref="A2:A44"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="B34:B44"/>
+    <mergeCell ref="A45:A76"/>
+    <mergeCell ref="B65:B76"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B45:B54"/>
+    <mergeCell ref="B55:B64"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
